--- a/data/trans_camb/P2A_ner_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P2A_ner_R-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,33; -2,19</t>
+          <t>-12,21; -2,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,06; 11,13</t>
+          <t>-4,43; 11,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 11,69</t>
+          <t>-4,69; 12,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-15,92; -2,35</t>
+          <t>-14,72; -2,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-13,7; 1,01</t>
+          <t>-13,16; 0,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,79; 9,4</t>
+          <t>-7,04; 9,41</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-10,82; -3,03</t>
+          <t>-10,75; -3,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,15; 3,74</t>
+          <t>-6,77; 3,88</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 7,9</t>
+          <t>-3,59; 8,18</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-76,04; 457,48</t>
+          <t>-72,34; 534,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-60,04; 535,46</t>
+          <t>-72,48; 442,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -13,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 95,54</t>
+          <t>-100,0; 60,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-66,74; 243,9</t>
+          <t>-65,19; 235,6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -56,36</t>
+          <t>-100,0; -55,97</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-78,25; 95,72</t>
+          <t>-76,48; 93,3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-42,57; 186,63</t>
+          <t>-39,36; 229,1</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 4,6</t>
+          <t>0,08; 4,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,85; 6,32</t>
+          <t>1,75; 6,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,3; 6,87</t>
+          <t>2,48; 7,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 1,34</t>
+          <t>-1,69; 1,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,1; 5,47</t>
+          <t>1,0; 5,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,5; 6,94</t>
+          <t>2,47; 7,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 2,11</t>
+          <t>-0,34; 2,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,08; 5,24</t>
+          <t>2,02; 5,31</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,15; 6,43</t>
+          <t>3,07; 6,33</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,42; 512,43</t>
+          <t>-7,01; 519,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>53,87; 721,41</t>
+          <t>52,14; 843,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>76,12; 868,48</t>
+          <t>82,48; 932,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-68,92; 143,87</t>
+          <t>-66,37; 154,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>32,93; 522,08</t>
+          <t>27,26; 485,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,95; 676,6</t>
+          <t>74,75; 644,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-19,88; 161,81</t>
+          <t>-19,62; 178,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>87,71; 472,43</t>
+          <t>77,41; 426,61</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>121,43; 543,12</t>
+          <t>122,79; 527,04</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 3,78</t>
+          <t>-2,69; 3,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 3,51</t>
+          <t>-2,07; 3,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 1,8</t>
+          <t>-3,18; 1,8</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 0,15</t>
+          <t>-5,38; 0,49</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 5,91</t>
+          <t>-2,39; 5,82</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 2,34</t>
+          <t>-4,42; 2,18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 1,08</t>
+          <t>-3,29; 1,06</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 3,73</t>
+          <t>-1,23; 3,85</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 1,34</t>
+          <t>-2,56; 1,45</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-88,24; 561,28</t>
+          <t>-100,0; 554,06</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-71,76; 481,02</t>
+          <t>-72,92; 570,14</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-90,87; 334,57</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 94,88</t>
+          <t>-100,0; 148,78</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-54,16; 396,69</t>
+          <t>-57,2; 376,75</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-77,28; 182,34</t>
+          <t>-83,05; 152,56</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-80,7; 85,24</t>
+          <t>-84,35; 75,53</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-42,52; 239,22</t>
+          <t>-38,44; 278,05</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-71,72; 104,15</t>
+          <t>-69,13; 121,12</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 2,54</t>
+          <t>-0,82; 2,5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,05; 4,86</t>
+          <t>0,99; 4,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,32; 5,17</t>
+          <t>1,47; 5,02</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,86; -0,02</t>
+          <t>-2,64; -0,01</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,29; 3,88</t>
+          <t>0,24; 3,91</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,14; 5,06</t>
+          <t>1,29; 4,83</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 0,74</t>
+          <t>-1,36; 0,73</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,81</t>
+          <t>1,08; 3,65</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,78; 4,45</t>
+          <t>1,84; 4,4</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-26,92; 162,54</t>
+          <t>-30,3; 154,55</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>31,39; 321,6</t>
+          <t>22,01; 305,45</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>39,75; 328,49</t>
+          <t>43,13; 344,41</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-79,12; 3,74</t>
+          <t>-76,48; 7,11</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,51; 207,97</t>
+          <t>5,83; 202,8</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>31,01; 269,31</t>
+          <t>35,55; 239,55</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-44,46; 38,9</t>
+          <t>-46,46; 37,6</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>38,33; 195,61</t>
+          <t>35,97; 184,39</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>58,57; 229,9</t>
+          <t>59,68; 230,47</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_ner_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P2A_ner_R-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,21; -2,18</t>
+          <t>-12,27; -2,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 11,63</t>
+          <t>-4,72; 11,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 12,12</t>
+          <t>-4,73; 12,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,72; -2,49</t>
+          <t>-14,67; -1,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-13,16; 0,85</t>
+          <t>-12,79; 1,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,04; 9,41</t>
+          <t>-7,5; 10,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-10,75; -3,0</t>
+          <t>-11,05; -3,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 3,88</t>
+          <t>-7,28; 3,92</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 8,18</t>
+          <t>-3,86; 7,95</t>
         </is>
       </c>
     </row>
@@ -788,12 +788,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-72,34; 534,2</t>
+          <t>-66,58; 511,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-72,48; 442,47</t>
+          <t>-72,89; 482,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -803,27 +803,27 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 60,04</t>
+          <t>-100,0; 98,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-65,19; 235,6</t>
+          <t>-62,79; 311,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -55,97</t>
+          <t>-100,0; -39,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-76,48; 93,3</t>
+          <t>-73,54; 120,74</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-39,36; 229,1</t>
+          <t>-45,98; 188,88</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,08; 4,3</t>
+          <t>0,08; 4,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,75; 6,6</t>
+          <t>1,66; 6,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,48; 7,17</t>
+          <t>2,47; 7,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 1,41</t>
+          <t>-1,81; 1,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 5,47</t>
+          <t>1,18; 5,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,47; 7,17</t>
+          <t>2,5; 7,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 2,23</t>
+          <t>-0,35; 2,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,02; 5,31</t>
+          <t>1,96; 5,03</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,07; 6,33</t>
+          <t>3,03; 6,33</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,01; 519,06</t>
+          <t>-7,47; 503,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>52,14; 843,77</t>
+          <t>59,82; 796,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>82,48; 932,77</t>
+          <t>87,8; 770,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-66,37; 154,95</t>
+          <t>-68,77; 181,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,26; 485,97</t>
+          <t>30,37; 486,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,75; 644,73</t>
+          <t>74,13; 677,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-19,62; 178,45</t>
+          <t>-15,88; 198,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>77,41; 426,61</t>
+          <t>79,44; 430,57</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>122,79; 527,04</t>
+          <t>114,4; 522,36</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 3,77</t>
+          <t>-2,27; 4,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 3,82</t>
+          <t>-2,26; 3,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 1,8</t>
+          <t>-3,13; 1,88</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 0,49</t>
+          <t>-5,43; 0,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 5,82</t>
+          <t>-2,4; 5,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 2,18</t>
+          <t>-4,69; 2,11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 1,06</t>
+          <t>-3,02; 1,13</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 3,85</t>
+          <t>-1,21; 3,89</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 1,45</t>
+          <t>-2,49; 1,41</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 554,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-72,92; 570,14</t>
+          <t>-77,4; 651,01</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-90,87; 334,57</t>
+          <t>-87,98; 354,57</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 148,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-57,2; 376,75</t>
+          <t>-56,44; 352,51</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-83,05; 152,56</t>
+          <t>-85,57; 179,49</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-84,35; 75,53</t>
+          <t>-80,4; 91,29</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-38,44; 278,05</t>
+          <t>-37,07; 247,35</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-69,13; 121,12</t>
+          <t>-67,12; 111,77</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 2,5</t>
+          <t>-0,65; 2,52</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,99; 4,77</t>
+          <t>1,1; 4,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,47; 5,02</t>
+          <t>1,25; 5,01</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,64; -0,01</t>
+          <t>-2,78; 0,11</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,24; 3,91</t>
+          <t>0,31; 3,96</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,29; 4,83</t>
+          <t>1,23; 4,99</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 0,73</t>
+          <t>-1,39; 0,73</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,08; 3,65</t>
+          <t>1,11; 3,78</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,84; 4,4</t>
+          <t>1,88; 4,55</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-30,3; 154,55</t>
+          <t>-26,67; 173,05</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>22,01; 305,45</t>
+          <t>35,41; 337,16</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>43,13; 344,41</t>
+          <t>35,42; 330,79</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-76,48; 7,11</t>
+          <t>-76,8; 11,51</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,83; 202,8</t>
+          <t>1,29; 197,57</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,55; 239,55</t>
+          <t>33,31; 259,85</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-46,46; 37,6</t>
+          <t>-46,86; 36,23</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>35,97; 184,39</t>
+          <t>37,86; 204,28</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>59,68; 230,47</t>
+          <t>59,4; 227,36</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_ner_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P2A_ner_R-Estudios-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-7,09</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-5,25</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1,7</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-5,66</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>2,52</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2,95</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-7,09</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-5,25</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,06</t>
+          <t>4,5</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2,06</t>
+          <t>3,12</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,27; -2,15</t>
+          <t>-15,92; -2,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 11,66</t>
+          <t>-13,7; 1,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 12,63</t>
+          <t>-7,26; 10,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,67; -1,91</t>
+          <t>-11,33; -2,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,79; 1,28</t>
+          <t>-5,06; 11,13</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 10,34</t>
+          <t>-3,63; 14,6</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-11,05; -3,0</t>
+          <t>-10,82; -3,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 3,92</t>
+          <t>-7,15; 3,74</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 7,95</t>
+          <t>-3,05; 9,38</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-91,13%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-67,43%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>21,86%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>44,41%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>52,14%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-91,13%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-67,43%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>79,41%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>46,71%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>-100,0; -13,77</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>-100,0; 95,54</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>-63,42; 263,25</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-66,58; 511,23</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-72,89; 482,38</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 98,59</t>
+          <t>-76,04; 457,48</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-62,79; 311,47</t>
+          <t>-53,77; 593,35</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -39,77</t>
+          <t>-100,0; -56,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-73,54; 120,74</t>
+          <t>-78,25; 95,72</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-45,98; 188,88</t>
+          <t>-37,02; 221,36</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,2</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3,23</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5,14</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>2,07</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>3,85</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>4,64</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,2</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>3,23</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,73</t>
+          <t>5,29</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>4,68</t>
+          <t>5,21</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,08; 4,43</t>
+          <t>-1,79; 1,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,66; 6,41</t>
+          <t>1,1; 5,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,47; 7,08</t>
+          <t>2,9; 7,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 1,76</t>
+          <t>0,29; 4,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,18; 5,47</t>
+          <t>1,85; 6,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,5; 7,17</t>
+          <t>2,81; 7,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 2,34</t>
+          <t>-0,39; 2,11</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,96; 5,03</t>
+          <t>2,08; 5,24</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,03; 6,33</t>
+          <t>3,68; 7,07</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-10,85%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>175,28%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>279,12%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>126,68%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>235,55%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>283,64%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-10,85%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>175,28%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>256,73%</t>
+          <t>323,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>268,46%</t>
+          <t>298,39%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 503,21</t>
+          <t>-68,92; 143,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>59,82; 796,0</t>
+          <t>32,93; 522,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>87,8; 770,2</t>
+          <t>94,95; 722,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-68,77; 181,55</t>
+          <t>0,42; 512,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>30,37; 486,63</t>
+          <t>53,87; 721,41</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,13; 677,67</t>
+          <t>96,96; 926,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-15,88; 198,62</t>
+          <t>-19,88; 161,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>79,44; 430,57</t>
+          <t>87,71; 472,43</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>114,4; 522,36</t>
+          <t>138,52; 583,54</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-2,17</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1,48</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-0,96</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>0,47</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0,81</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,36</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-2,17</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,48</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-0,76</t>
+          <t>-0,25</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,49</t>
+          <t>-0,56</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 4,0</t>
+          <t>-5,54; 0,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 3,99</t>
+          <t>-2,37; 5,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 1,88</t>
+          <t>-4,46; 1,74</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 0,45</t>
+          <t>-2,25; 3,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 5,43</t>
+          <t>-2,16; 3,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 2,11</t>
+          <t>-3,15; 1,9</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 1,13</t>
+          <t>-3,04; 1,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 3,89</t>
+          <t>-1,33; 3,73</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 1,41</t>
+          <t>-2,77; 1,19</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-68,05%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>46,48%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-30,11%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>23,82%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>40,7%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-18,22%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-68,05%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>46,48%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-23,91%</t>
+          <t>-12,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-19,22%</t>
+          <t>-21,82%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 94,88</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>-54,16; 396,69</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>-80,52; 140,57</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>-88,24; 561,28</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>-71,76; 481,02</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-77,4; 651,01</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-87,98; 354,57</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-56,44; 352,51</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-85,57; 179,49</t>
-        </is>
-      </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-80,4; 91,29</t>
+          <t>-80,7; 85,24</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-37,07; 247,35</t>
+          <t>-42,52; 239,22</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-67,12; 111,77</t>
+          <t>-72,42; 84,05</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-1,36</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2,01</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3,31</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>0,79</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>2,82</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>3,24</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-1,36</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2,01</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,02</t>
+          <t>3,75</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3,14</t>
+          <t>3,52</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 2,52</t>
+          <t>-2,86; -0,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,1; 4,81</t>
+          <t>0,29; 3,88</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,25; 5,01</t>
+          <t>1,39; 5,46</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 0,11</t>
+          <t>-0,74; 2,54</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,96</t>
+          <t>1,05; 4,86</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,23; 4,99</t>
+          <t>1,77; 5,56</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 0,73</t>
+          <t>-1,34; 0,74</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,11; 3,78</t>
+          <t>1,19; 3,81</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,88; 4,55</t>
+          <t>2,13; 4,92</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-49,76%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>73,52%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>120,94%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>36,1%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>128,97%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>148,25%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-49,76%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>73,52%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>110,54%</t>
+          <t>171,42%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>127,13%</t>
+          <t>142,82%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-26,67; 173,05</t>
+          <t>-79,12; 3,74</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>35,41; 337,16</t>
+          <t>4,51; 207,97</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>35,42; 330,79</t>
+          <t>33,89; 288,52</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-76,8; 11,51</t>
+          <t>-26,92; 162,54</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,29; 197,57</t>
+          <t>31,39; 321,6</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>33,31; 259,85</t>
+          <t>53,11; 380,78</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-46,86; 36,23</t>
+          <t>-44,46; 38,9</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>37,86; 204,28</t>
+          <t>38,33; 195,61</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>59,4; 227,36</t>
+          <t>70,27; 258,56</t>
         </is>
       </c>
     </row>
